--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R3" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,7 +850,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -855,7 +860,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,29 +874,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,42 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R4" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -971,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,18 +984,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1197,45 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130336154</v>
+        <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511078</v>
+        <v>511153</v>
       </c>
       <c r="R7" t="n">
-        <v>6746730</v>
+        <v>6746738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,57 +1282,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341473</v>
+        <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511153</v>
+        <v>511078</v>
       </c>
       <c r="R8" t="n">
-        <v>6746738</v>
+        <v>6746730</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,9 +1362,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1644,19 +1644,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R11" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,52 +1683,36 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -1760,16 +1741,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R12" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,29 +1783,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2151,6 +2151,501 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130347965</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>510950</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6746659</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130347958</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97797</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>511073</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6746715</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>20 m3</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130347954</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>511013</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6746799</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två tallar med gamla ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130347963</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>511152</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6746765</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130347964</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>511145</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6746722</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R3" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,7 +845,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -860,12 +855,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,28 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +894,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R4" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +961,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +971,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +985,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1197,45 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341473</v>
+        <v>130336154</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511153</v>
+        <v>511078</v>
       </c>
       <c r="R7" t="n">
-        <v>6746738</v>
+        <v>6746730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,9 +1265,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,57 +1292,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130336154</v>
+        <v>130341473</v>
       </c>
       <c r="B8" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511078</v>
+        <v>511153</v>
       </c>
       <c r="R8" t="n">
-        <v>6746730</v>
+        <v>6746738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,19 +1372,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1508,45 +1508,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130336304</v>
+        <v>130340206</v>
       </c>
       <c r="B10" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511111</v>
+        <v>511123</v>
       </c>
       <c r="R10" t="n">
-        <v>6746701</v>
+        <v>6746762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,7 +1581,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1588,7 +1591,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,63 +1605,64 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341474</v>
+        <v>130336304</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511148</v>
+        <v>511111</v>
       </c>
       <c r="R11" t="n">
-        <v>6746741</v>
+        <v>6746701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,9 +1692,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,19 +1719,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B12" t="n">
         <v>79180</v>
@@ -1741,19 +1760,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R12" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,45 +1799,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R3" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,7 +850,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -855,7 +860,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,29 +874,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,42 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R4" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -971,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,18 +984,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1508,48 +1508,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130340206</v>
+        <v>130336304</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511123</v>
+        <v>511111</v>
       </c>
       <c r="R10" t="n">
-        <v>6746762</v>
+        <v>6746701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,7 +1578,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1591,12 +1588,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,26 +1597,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1653,16 +1644,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R11" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,74 +1686,90 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130336304</v>
+        <v>130341474</v>
       </c>
       <c r="B12" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511111</v>
+        <v>511148</v>
       </c>
       <c r="R12" t="n">
-        <v>6746701</v>
+        <v>6746741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,19 +1799,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,12 +1816,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -1508,45 +1508,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130336304</v>
+        <v>130340206</v>
       </c>
       <c r="B10" t="n">
-        <v>97791</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511111</v>
+        <v>511123</v>
       </c>
       <c r="R10" t="n">
-        <v>6746701</v>
+        <v>6746762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,7 +1581,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1588,7 +1591,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,25 +1605,26 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B11" t="n">
         <v>79180</v>
@@ -1644,19 +1653,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R11" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,90 +1692,74 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341474</v>
+        <v>130336304</v>
       </c>
       <c r="B12" t="n">
-        <v>79180</v>
+        <v>97791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511148</v>
+        <v>511111</v>
       </c>
       <c r="R12" t="n">
-        <v>6746741</v>
+        <v>6746701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,9 +1789,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,12 +1816,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R3" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,7 +845,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -860,12 +855,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,28 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +894,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R4" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +961,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +971,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +985,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341471</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>130341472</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130341470</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,48 +1508,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130340206</v>
+        <v>130336304</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>97794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511123</v>
+        <v>511111</v>
       </c>
       <c r="R10" t="n">
-        <v>6746762</v>
+        <v>6746701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,7 +1578,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1591,12 +1588,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,29 +1597,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,16 +1644,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R11" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,74 +1686,90 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130336304</v>
+        <v>130341474</v>
       </c>
       <c r="B12" t="n">
-        <v>97791</v>
+        <v>79183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511111</v>
+        <v>511148</v>
       </c>
       <c r="R12" t="n">
-        <v>6746701</v>
+        <v>6746741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,19 +1799,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,12 +1816,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>130336285</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130347965</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>130347963</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>130347964</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341471</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>130340197</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130341472</v>
+        <v>130341470</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511140</v>
+        <v>511100</v>
       </c>
       <c r="R5" t="n">
-        <v>6746792</v>
+        <v>6746788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130341470</v>
+        <v>130341472</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511100</v>
+        <v>511140</v>
       </c>
       <c r="R6" t="n">
-        <v>6746788</v>
+        <v>6746792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
         <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,45 +1508,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130336304</v>
+        <v>130341474</v>
       </c>
       <c r="B10" t="n">
-        <v>97794</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511111</v>
+        <v>511148</v>
       </c>
       <c r="R10" t="n">
-        <v>6746701</v>
+        <v>6746741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,19 +1576,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,60 +1593,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130340206</v>
+        <v>130336304</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>97820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511123</v>
+        <v>511111</v>
       </c>
       <c r="R11" t="n">
-        <v>6746762</v>
+        <v>6746701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1675,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1698,12 +1685,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1712,29 +1694,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B12" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,16 +1741,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R12" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,29 +1783,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>130336285</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130347965</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>130347954</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>130347963</v>
       </c>
       <c r="B19" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>130347964</v>
       </c>
       <c r="B20" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R3" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,7 +850,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -855,7 +860,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,29 +874,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,42 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R4" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -971,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,18 +984,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130341470</v>
+        <v>130341472</v>
       </c>
       <c r="B5" t="n">
         <v>79209</v>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511100</v>
+        <v>511140</v>
       </c>
       <c r="R5" t="n">
-        <v>6746788</v>
+        <v>6746792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130341472</v>
+        <v>130341470</v>
       </c>
       <c r="B6" t="n">
         <v>79209</v>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511140</v>
+        <v>511100</v>
       </c>
       <c r="R6" t="n">
-        <v>6746792</v>
+        <v>6746788</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,45 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341473</v>
+        <v>130336154</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>97821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511153</v>
+        <v>511078</v>
       </c>
       <c r="R7" t="n">
-        <v>6746738</v>
+        <v>6746730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,9 +1265,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,57 +1292,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130336154</v>
+        <v>130341473</v>
       </c>
       <c r="B8" t="n">
-        <v>97820</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511078</v>
+        <v>511153</v>
       </c>
       <c r="R8" t="n">
-        <v>6746730</v>
+        <v>6746738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,19 +1372,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1508,45 +1508,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130341474</v>
+        <v>130336304</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>97821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511148</v>
+        <v>511111</v>
       </c>
       <c r="R10" t="n">
-        <v>6746741</v>
+        <v>6746701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,9 +1576,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,57 +1603,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130336304</v>
+        <v>130340206</v>
       </c>
       <c r="B11" t="n">
-        <v>97820</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511111</v>
+        <v>511123</v>
       </c>
       <c r="R11" t="n">
-        <v>6746701</v>
+        <v>6746762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,7 +1688,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1685,7 +1698,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,25 +1712,26 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B12" t="n">
         <v>79209</v>
@@ -1741,19 +1760,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R12" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,45 +1799,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R3" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,7 +845,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -860,12 +855,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,28 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +894,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R4" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +961,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +971,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +985,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1197,45 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130336154</v>
+        <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>97821</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511078</v>
+        <v>511153</v>
       </c>
       <c r="R7" t="n">
-        <v>6746730</v>
+        <v>6746738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,57 +1282,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341473</v>
+        <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>97822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511153</v>
+        <v>511078</v>
       </c>
       <c r="R8" t="n">
-        <v>6746738</v>
+        <v>6746730</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,9 +1362,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
         <v>130336304</v>
       </c>
       <c r="B10" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341471</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>130340197</v>
       </c>
       <c r="B4" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>130341472</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130341470</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>130336304</v>
       </c>
       <c r="B10" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>130340206</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>130341474</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>130336285</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130347965</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>130347954</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>130347963</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>130347964</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R3" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,7 +850,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -855,7 +860,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,29 +874,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,42 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R4" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -971,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,18 +984,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
         <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,45 +1508,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130336304</v>
+        <v>130340206</v>
       </c>
       <c r="B10" t="n">
-        <v>97824</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511111</v>
+        <v>511123</v>
       </c>
       <c r="R10" t="n">
-        <v>6746701</v>
+        <v>6746762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,7 +1581,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1588,7 +1591,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,25 +1605,26 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B11" t="n">
         <v>79211</v>
@@ -1644,19 +1653,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R11" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,90 +1692,74 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341474</v>
+        <v>130336304</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>97828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511148</v>
+        <v>511111</v>
       </c>
       <c r="R12" t="n">
-        <v>6746741</v>
+        <v>6746701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,9 +1789,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,12 +1816,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R3" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,7 +845,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -860,12 +855,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,28 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +894,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R4" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +961,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +971,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +985,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -1197,45 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341473</v>
+        <v>130336154</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>97828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511153</v>
+        <v>511078</v>
       </c>
       <c r="R7" t="n">
-        <v>6746738</v>
+        <v>6746730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,9 +1265,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,57 +1292,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130336154</v>
+        <v>130341473</v>
       </c>
       <c r="B8" t="n">
-        <v>97828</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511078</v>
+        <v>511153</v>
       </c>
       <c r="R8" t="n">
-        <v>6746730</v>
+        <v>6746738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,19 +1372,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B10" t="n">
         <v>79211</v>
@@ -1537,19 +1537,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R10" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1579,52 +1576,36 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B11" t="n">
         <v>79211</v>
@@ -1653,16 +1634,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R11" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,29 +1676,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -1197,45 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130336154</v>
+        <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>97828</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511078</v>
+        <v>511153</v>
       </c>
       <c r="R7" t="n">
-        <v>6746730</v>
+        <v>6746738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,57 +1282,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341473</v>
+        <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>97828</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511153</v>
+        <v>511078</v>
       </c>
       <c r="R8" t="n">
-        <v>6746738</v>
+        <v>6746730</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,9 +1362,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B10" t="n">
         <v>79211</v>
@@ -1537,16 +1537,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R10" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,36 +1579,52 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B11" t="n">
         <v>79211</v>
@@ -1634,19 +1653,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R11" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,45 +1692,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341471</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>130340197</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>130341472</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130341470</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>130340206</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,45 +1624,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341474</v>
+        <v>130336304</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>97841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511148</v>
+        <v>511111</v>
       </c>
       <c r="R11" t="n">
-        <v>6746741</v>
+        <v>6746701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,9 +1692,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,57 +1719,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130336304</v>
+        <v>130341474</v>
       </c>
       <c r="B12" t="n">
-        <v>97828</v>
+        <v>79219</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511111</v>
+        <v>511148</v>
       </c>
       <c r="R12" t="n">
-        <v>6746701</v>
+        <v>6746741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,19 +1799,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,12 +1816,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>130336285</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130347965</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97834</v>
+        <v>97847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>130347954</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>130347963</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>130347964</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341471</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R3" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,7 +850,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -855,7 +860,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -864,29 +874,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B4" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,42 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R4" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -971,12 +975,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,18 +984,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
         <v>130341472</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130341470</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,48 +1508,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130340206</v>
+        <v>130336304</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>97842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511123</v>
+        <v>511111</v>
       </c>
       <c r="R10" t="n">
-        <v>6746762</v>
+        <v>6746701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,7 +1578,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1591,12 +1588,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,64 +1597,63 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130336304</v>
+        <v>130341474</v>
       </c>
       <c r="B11" t="n">
-        <v>97841</v>
+        <v>79220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511111</v>
+        <v>511148</v>
       </c>
       <c r="R11" t="n">
-        <v>6746701</v>
+        <v>6746741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,19 +1683,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,22 +1700,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,16 +1741,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R12" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,29 +1783,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>130336285</v>
       </c>
       <c r="B15" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130347965</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97847</v>
+        <v>97848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>130347954</v>
       </c>
       <c r="B18" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>130347963</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>130347964</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130341471</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340197</v>
+        <v>130336407</v>
       </c>
       <c r="B3" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510999</v>
+        <v>511123</v>
       </c>
       <c r="R3" t="n">
-        <v>6746688</v>
+        <v>6746783</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,7 +845,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -860,12 +855,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre spår</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,28 +864,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130336407</v>
+        <v>130340197</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +894,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511123</v>
+        <v>510999</v>
       </c>
       <c r="R4" t="n">
-        <v>6746783</v>
+        <v>6746688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +961,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -975,7 +971,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,19 +985,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
         <v>130341472</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130341470</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,45 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341473</v>
+        <v>130336154</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>97845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511153</v>
+        <v>511078</v>
       </c>
       <c r="R7" t="n">
-        <v>6746738</v>
+        <v>6746730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,9 +1265,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,57 +1292,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130336154</v>
+        <v>130341473</v>
       </c>
       <c r="B8" t="n">
-        <v>97842</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511078</v>
+        <v>511153</v>
       </c>
       <c r="R8" t="n">
-        <v>6746730</v>
+        <v>6746738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,19 +1372,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
         <v>130336304</v>
       </c>
       <c r="B10" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1615,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,16 +1644,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R11" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,39 +1686,55 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B12" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,19 +1760,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R12" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,45 +1799,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>130336258</v>
       </c>
       <c r="B14" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>130336285</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>130347965</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>130347958</v>
       </c>
       <c r="B17" t="n">
-        <v>97848</v>
+        <v>97851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>130347954</v>
       </c>
       <c r="B18" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>130347963</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>130347964</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -1197,45 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130336154</v>
+        <v>130341473</v>
       </c>
       <c r="B7" t="n">
-        <v>97845</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511078</v>
+        <v>511153</v>
       </c>
       <c r="R7" t="n">
-        <v>6746730</v>
+        <v>6746738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,57 +1282,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341473</v>
+        <v>130336154</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>97845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511153</v>
+        <v>511078</v>
       </c>
       <c r="R8" t="n">
-        <v>6746738</v>
+        <v>6746730</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,9 +1362,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -1508,45 +1508,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130336304</v>
+        <v>130340206</v>
       </c>
       <c r="B10" t="n">
-        <v>97845</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511111</v>
+        <v>511123</v>
       </c>
       <c r="R10" t="n">
-        <v>6746701</v>
+        <v>6746762</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,7 +1581,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1588,7 +1591,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,25 +1605,26 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130340206</v>
+        <v>130341474</v>
       </c>
       <c r="B11" t="n">
         <v>79221</v>
@@ -1644,19 +1653,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511123</v>
+        <v>511148</v>
       </c>
       <c r="R11" t="n">
-        <v>6746762</v>
+        <v>6746741</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,90 +1692,74 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130341474</v>
+        <v>130336304</v>
       </c>
       <c r="B12" t="n">
-        <v>79221</v>
+        <v>97845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511148</v>
+        <v>511111</v>
       </c>
       <c r="R12" t="n">
-        <v>6746741</v>
+        <v>6746701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,9 +1789,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,12 +1816,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 61678-2025 artfynd.xlsx
+++ b/artfynd/A 61678-2025 artfynd.xlsx
@@ -1508,48 +1508,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130340206</v>
+        <v>130336304</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>97845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Långbromyren, Långbromyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511123</v>
+        <v>511111</v>
       </c>
       <c r="R10" t="n">
-        <v>6746762</v>
+        <v>6746701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,7 +1578,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1591,12 +1588,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,26 +1597,25 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130341474</v>
+        <v>130340206</v>
       </c>
       <c r="B11" t="n">
         <v>79221</v>
@@ -1653,16 +1644,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511148</v>
+        <v>511123</v>
       </c>
       <c r="R11" t="n">
-        <v>6746741</v>
+        <v>6746762</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,74 +1686,90 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130336304</v>
+        <v>130341474</v>
       </c>
       <c r="B12" t="n">
-        <v>97845</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långbromyren, Långbromyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511111</v>
+        <v>511148</v>
       </c>
       <c r="R12" t="n">
-        <v>6746701</v>
+        <v>6746741</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,19 +1799,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,12 +1816,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
